--- a/tabulka-smutek.xlsx
+++ b/tabulka-smutek.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1414F89E-7579-4FF5-91D9-B0E6AD87BF5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F18AD8EB-D833-427C-B45C-86B5F9310027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24465" yWindow="3975" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="1" r:id="rId1"/>
@@ -26,9 +26,6 @@
     <t>Tro/. chu/. mě/. to/. mr/. zí/-</t>
   </si>
   <si>
-    <t>Nic/. se/. mi/. nech/. ce/. dě/. lat/.</t>
-  </si>
-  <si>
     <t>Cí/- tím/- se/. u/. na/. ve/. ný/-</t>
   </si>
   <si>
@@ -330,18 +327,29 @@
       </rPr>
       <t>mrzí</t>
     </r>
+  </si>
+  <si>
+    <t>Nic/. se/. mi/. ne/. chce/. dě/. lat/.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -384,7 +392,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
@@ -733,7 +741,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -741,7 +749,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
@@ -749,31 +757,31 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
         <v>2</v>
@@ -781,34 +789,34 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
